--- a/output/pdf_financials_xlsx/EONE.xlsx
+++ b/output/pdf_financials_xlsx/EONE.xlsx
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.06585299999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06585299999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.067953</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.295709</v>
       </c>
     </row>
     <row r="93">
@@ -2426,10 +2426,10 @@
         <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.217374</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.189544</v>
       </c>
     </row>
     <row r="104">
@@ -2483,10 +2483,10 @@
         <v>0.061485</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.06263299999999999</v>
+        <v>-0.154741</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.241402</v>
+        <v>0.430946</v>
       </c>
     </row>
     <row r="107">
@@ -3198,7 +3198,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -3500,7 +3504,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3790,7 +3798,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3974,7 +3986,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4442,7 +4458,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.06585299999999999</v>
       </c>
@@ -4554,7 +4574,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -5402,7 +5426,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EONE.xlsx
+++ b/output/pdf_financials_xlsx/EONE.xlsx
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.160958</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.027327</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.171446</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.115411</v>
       </c>
     </row>
     <row r="35">
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.160958</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.027327</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.171446</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.115411</v>
       </c>
     </row>
     <row r="37">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.172328</v>
+        <v>0.01137</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.036766</v>
+        <v>0.009438999999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.421475</v>
+        <v>0.250029</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.210003</v>
+        <v>0.094592</v>
       </c>
     </row>
     <row r="49">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">

--- a/output/pdf_financials_xlsx/EONE.xlsx
+++ b/output/pdf_financials_xlsx/EONE.xlsx
@@ -6014,7 +6014,11 @@
           <t>Issuance of shares - private placement</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>0.175</v>
       </c>
